--- a/erp-server/erp-server-wms/src/main/resources/excel/subcontractIssue.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/subcontractIssue.xlsx
@@ -80,55 +80,55 @@
     <t>审核完成时间</t>
   </si>
   <si>
-    <t>.{code}</t>
-  </si>
-  <si>
-    <t>.{sourceCode}</t>
-  </si>
-  <si>
-    <t>.{approveStatusName}</t>
-  </si>
-  <si>
-    <t>.{invalidStatusName}</t>
-  </si>
-  <si>
-    <t>.{typeName}</t>
-  </si>
-  <si>
-    <t>.{skuNo}</t>
-  </si>
-  <si>
-    <t>.{productName}</t>
-  </si>
-  <si>
-    <t>.{date}</t>
-  </si>
-  <si>
-    <t>.{receiveQty}</t>
-  </si>
-  <si>
-    <t>.{issueQty}</t>
-  </si>
-  <si>
-    <t>.{warehouseName}</t>
-  </si>
-  <si>
-    <t>.{warehouseLocationName}</t>
-  </si>
-  <si>
-    <t>.{remark}</t>
-  </si>
-  <si>
-    <t>.{approveUserName}</t>
-  </si>
-  <si>
-    <t>.{createUserName}</t>
-  </si>
-  <si>
-    <t>.{createTime}</t>
-  </si>
-  <si>
-    <t>.{approveTime}</t>
+    <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.invalidStatusName}</t>
+  </si>
+  <si>
+    <t>{.typeName}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.date}</t>
+  </si>
+  <si>
+    <t>{.receiveQty}</t>
+  </si>
+  <si>
+    <t>{.issueQty}</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.warehouseLocationName}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.approveTime}</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1076,7 @@
     <col min="12" max="12" width="12.125" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="15.875" customWidth="1"/>
-    <col min="15" max="15" width="11.375" customWidth="1"/>
+    <col min="15" max="15" width="14.125" customWidth="1"/>
     <col min="16" max="16" width="15.375" customWidth="1"/>
     <col min="17" max="17" width="12.625" customWidth="1"/>
   </cols>

--- a/erp-server/erp-server-wms/src/main/resources/excel/subcontractIssue.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/subcontractIssue.xlsx
@@ -83,7 +83,7 @@
     <t>{.code}</t>
   </si>
   <si>
-    <t>{.sourceCode}</t>
+    <t>{.subcontractOrderCode}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -1062,17 +1062,17 @@
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="10.625" customWidth="1"/>
-    <col min="2" max="2" width="13.75" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="17.375" customWidth="1"/>
+    <col min="3" max="3" width="17.25" customWidth="1"/>
     <col min="4" max="4" width="15.375" customWidth="1"/>
     <col min="5" max="5" width="13.75" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="18.125" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
     <col min="8" max="8" width="13.875" customWidth="1"/>
     <col min="9" max="9" width="13.5" customWidth="1"/>
     <col min="10" max="10" width="13.25" customWidth="1"/>
-    <col min="11" max="11" width="16.875" customWidth="1"/>
+    <col min="11" max="11" width="28.75" customWidth="1"/>
     <col min="12" max="12" width="12.125" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="15.875" customWidth="1"/>
